--- a/DataTables/DetailText/剧情/000_04好消息.xlsx
+++ b/DataTables/DetailText/剧情/000_04好消息.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F1EC26-F968-475D-8CC4-4D17D75F3970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB990C-3318-443C-A134-23861E0A059A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="6150" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -456,7 +443,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -667,7 +654,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -685,7 +672,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
@@ -747,7 +734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>43</v>
       </c>
@@ -757,7 +744,9 @@
       <c r="C2" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="23">
+        <v>1</v>
+      </c>
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
@@ -1124,7 +1113,7 @@
       </c>
       <c r="I4" s="28"/>
     </row>
-    <row r="5" spans="1:9" ht="33">
+    <row r="5" spans="1:9" ht="30">
       <c r="A5" s="1">
         <v>4</v>
       </c>

--- a/DataTables/DetailText/剧情/000_04好消息.xlsx
+++ b/DataTables/DetailText/剧情/000_04好消息.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB990C-3318-443C-A134-23861E0A059A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6731CAB-20EC-48B7-9A36-97B7F13A7544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -184,14 +197,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>一千两也不是个小数目，但总归是有盼头了…</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>我还去找了胡承龙，他答应出资帮您出书。再加上这些年您医治的病人，咱家的亲戚朋友，也有愿意出钱帮忙的，咱们只要再凑一千两就可以出版此书。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>000_04</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -201,6 +206,14 @@
   </si>
   <si>
     <t>Music</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>我还去找了胡承龙，他答应出资帮您出书。再加上这些年您医治的病人，咱家的亲戚朋友，也有愿意出钱帮忙的，咱们只要再凑六百两就可以出版此书。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>六百也不是个小数目，但总归是有盼头了…</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -443,7 +456,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -654,7 +667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -672,7 +685,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
@@ -734,9 +747,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>33</v>
@@ -753,7 +766,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="22"/>
       <c r="J2" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
@@ -1047,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1113,7 +1126,7 @@
       </c>
       <c r="I4" s="28"/>
     </row>
-    <row r="5" spans="1:9" ht="30">
+    <row r="5" spans="1:9" ht="33">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1130,7 +1143,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="28"/>
     </row>
@@ -1153,7 +1166,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="27" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I6" s="28"/>
     </row>

--- a/DataTables/DetailText/剧情/000_04好消息.xlsx
+++ b/DataTables/DetailText/剧情/000_04好消息.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6731CAB-20EC-48B7-9A36-97B7F13A7544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A188655-02F8-4BCC-90E1-0BEE898CFD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -456,7 +456,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -667,7 +667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -685,7 +685,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
@@ -747,7 +747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>41</v>
       </c>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I4" s="28"/>
     </row>
-    <row r="5" spans="1:9" ht="33">
+    <row r="5" spans="1:9" ht="30">
       <c r="A5" s="1">
         <v>4</v>
       </c>
